--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,45 +807,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89976105</v>
+        <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>98215</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>569</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Bredmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626519</v>
+        <v>626425</v>
       </c>
       <c r="R3" t="n">
-        <v>6631702</v>
+        <v>6632382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2003-08-13</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2003-08-13</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Litet bestånd.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,74 +907,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89976105</t>
+          <t>https://artportalen.se/Sighting/137084688</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74811574</v>
+        <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>80467</v>
+        <v>92117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>dm²</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Bredmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626344</v>
+        <v>626374</v>
       </c>
       <c r="R4" t="n">
-        <v>6631739</v>
+        <v>6632425</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,17 +993,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2003-08-13</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2003-08-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2 dm2 på stammen av levande asp, omkr. 138 cm.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,41 +1019,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stammen av levande asp. # Asp</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74811574</t>
+          <t>https://artportalen.se/Sighting/137080859</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70080650</v>
+        <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>92117</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,21 +1051,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1073,21 +1073,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogstibble, Upl</t>
+          <t>Bredmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626184</v>
+        <v>626444</v>
       </c>
       <c r="R5" t="n">
-        <v>6631152</v>
+        <v>6632321</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1099,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Enköping</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1106,17 +1109,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Nysätra</t>
+          <t>Skogs-Tibble</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,23 +1138,1783 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Teresa Jonsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Teresa Jonsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137085262</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137084059</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92549</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>626433</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6632393</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137084059</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137085040</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92549</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>626417</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6632346</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137085040</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137085258</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92549</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>626444</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6632321</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137085258</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137085272</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92331</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3008</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Timmerticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>626441</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6632320</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137085272</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137084427</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93427</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>626435</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6632380</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137084427</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137080889</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92080</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>626425</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6632440</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080889</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137081807</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92080</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>626424</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6632421</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137081807</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137084761</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>626398</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6632408</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137084761</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137080237</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bredmossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>626384</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6632447</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080237</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137084324</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bredmossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>626425</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6632432</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137084324</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137081910</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>626431</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6632423</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137081910</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137084894</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>626405</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6632381</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137084894</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>89976105</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>569</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryopteris cristata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>626519</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6631702</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2003-08-13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2003-08-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Litet bestånd.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89976105</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>74811574</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>626344</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6631739</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2003-08-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2003-08-13</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2 dm2 på stammen av levande asp, omkr. 138 cm.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74811574</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>70080650</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Skogstibble, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>626184</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6631152</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Teresa Jonsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Teresa Jonsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/70080650</t>
         </is>
@@ -1153,6 +2926,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92331</v>
+        <v>92332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2250,11 +2250,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bredmossen, Skogstibble skjutfält, Upl</t>
@@ -2309,11 +2312,16 @@
           <t>15:55</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ganska säkra spår av födosökande tretåig hackspett på död gran där barken skalats av och många små hack och ”plockade” barkbitar nästan nere vid basen på trädet, vilket brukar vara typiskt för tretåig. Se bilder.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
@@ -2462,7 +2470,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92332</v>
+        <v>92338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92338</v>
+        <v>92342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92342</v>
+        <v>92344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92344</v>
+        <v>92357</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137080237</v>
       </c>
       <c r="B14" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>137084324</v>
       </c>
       <c r="B15" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137080237</v>
       </c>
       <c r="B14" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>137084324</v>
       </c>
       <c r="B15" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -1073,11 +1073,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bredmossen, Upl</t>
@@ -1306,11 +1302,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bredmossen, Upl</t>
@@ -1427,11 +1419,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bredmossen, Upl</t>
@@ -2008,11 +1996,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bredmossen, Upl</t>
@@ -2129,11 +2113,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bredmossen, Skogstibble skjutfält, Upl</t>
@@ -2252,11 +2232,7 @@
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2379,11 +2355,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bredmossen, Upl</t>
@@ -2500,11 +2472,7 @@
           <t>100</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bredmossen, Upl</t>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>137080237</v>
       </c>
       <c r="B14" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>137084324</v>
       </c>
       <c r="B15" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>137081910</v>
       </c>
       <c r="B16" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>137080237</v>
       </c>
       <c r="B14" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>137084324</v>
       </c>
       <c r="B15" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2083,7 +2083,7 @@
         <v>137080237</v>
       </c>
       <c r="B14" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>137084324</v>
       </c>
       <c r="B15" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -810,7 +810,7 @@
         <v>137084688</v>
       </c>
       <c r="B3" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137080859</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>137085262</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1160,7 +1160,7 @@
         <v>137084059</v>
       </c>
       <c r="B6" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>137085040</v>
       </c>
       <c r="B7" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>137085258</v>
       </c>
       <c r="B8" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137085272</v>
       </c>
       <c r="B9" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>137084427</v>
       </c>
       <c r="B10" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>137080889</v>
       </c>
       <c r="B11" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>137081807</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>137084761</v>
       </c>
       <c r="B13" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2442,7 +2442,7 @@
         <v>137084894</v>
       </c>
       <c r="B17" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 36350-2026 artfynd.xlsx
+++ b/artfynd/A 36350-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,42 +680,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69506266</v>
+        <v>137504113</v>
       </c>
       <c r="B2" t="n">
-        <v>87238</v>
+        <v>92186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>445</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>626681</v>
+        <v>626169</v>
       </c>
       <c r="R2" t="n">
-        <v>6632023</v>
+        <v>6632274</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,17 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-10-10</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-10-10</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>7 ex. under gran.</t>
+          <t>Ca. 5 dm2 på bark på granlåga, omkr. 85 cm, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,15 +778,24 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Äldre barrskog.</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr"/>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. 85 cm.. # Picea abies</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -801,16 +810,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69506266</t>
+          <t>https://artportalen.se/Sighting/137504113</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137084688</v>
+        <v>137504114</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>92186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,34 +827,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bredmossen, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>626425</v>
+        <v>626153</v>
       </c>
       <c r="R3" t="n">
-        <v>6632382</v>
+        <v>6632267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,27 +890,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Ca. 30 dm2 på bark på granlåga, omkr. 86 cm, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,31 +911,51 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. 86 cm.. # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137084688</t>
+          <t>https://artportalen.se/Sighting/137504114</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137080859</v>
+        <v>137504115</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,41 +963,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bredmossen, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>626374</v>
+        <v>626153</v>
       </c>
       <c r="R4" t="n">
-        <v>6632425</v>
+        <v>6632267</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,22 +1026,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:41</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ca. 15 dm2 på bark på granlåga, omkr. 86 cm, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,53 +1047,73 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. 86 cm.. # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137080859</t>
+          <t>https://artportalen.se/Sighting/137504115</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137085262</v>
+        <v>137504116</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>91694</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1357</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläckfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria sanguinea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1073,20 +1121,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bredmossen, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>626444</v>
+        <v>626142</v>
       </c>
       <c r="R5" t="n">
-        <v>6632321</v>
+        <v>6632239</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,22 +1162,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 ex. bland lövförna och gles mossvegetation, intill gran, asp och björk. Ca. 10 m ifrån avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,66 +1183,71 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137085262</t>
+          <t>https://artportalen.se/Sighting/137504116</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137084059</v>
+        <v>137504117</v>
       </c>
       <c r="B6" t="n">
-        <v>92617</v>
+        <v>92149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bredmossen, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>626433</v>
+        <v>626034</v>
       </c>
       <c r="R6" t="n">
-        <v>6632393</v>
+        <v>6632162</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,22 +1274,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:02</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:02</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På naken ved på granlåga, omkr. 33 cm.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,74 +1295,98 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Naken ved på granlåga, omkr. 33 cm. # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ebba Ganslandt</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ebba Ganslandt</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137084059</t>
+          <t>https://artportalen.se/Sighting/137504117</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137085040</v>
+        <v>69506266</v>
       </c>
       <c r="B7" t="n">
-        <v>92617</v>
+        <v>87238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bredmossen, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>626417</v>
+        <v>626681</v>
       </c>
       <c r="R7" t="n">
-        <v>6632346</v>
+        <v>6632023</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,22 +1410,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>1997-10-10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:45</t>
+          <t>1997-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>7 ex. under gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,30 +1432,41 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Äldre barrskog.</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137085040</t>
+          <t>https://artportalen.se/Sighting/69506266</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137085258</v>
+        <v>137504099</v>
       </c>
       <c r="B8" t="n">
-        <v>92617</v>
+        <v>92457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,21 +1474,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1419,20 +1496,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bredmossen, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>626444</v>
+        <v>626499</v>
       </c>
       <c r="R8" t="n">
-        <v>6632321</v>
+        <v>6632085</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,22 +1537,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 ex. på naken ved på granlåga, omkr. 88 cm, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,70 +1558,95 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Naken ved på granlåga, omkr. 88 cm.. # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137085258</t>
+          <t>https://artportalen.se/Sighting/137504099</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137085272</v>
+        <v>137504100</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3008</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bredmossen, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>626441</v>
+        <v>626571</v>
       </c>
       <c r="R9" t="n">
-        <v>6632320</v>
+        <v>6632106</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,22 +1673,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0,5 dm2 på bark på avbruten stamdel från granhögstubbe, omkr. 120 cm, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,31 +1694,51 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark på avbruten stamdel från granhögstubbe, omkr. 120 cm.. # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137085272</t>
+          <t>https://artportalen.se/Sighting/137504100</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137084427</v>
+        <v>137504101</v>
       </c>
       <c r="B10" t="n">
-        <v>93497</v>
+        <v>92618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1630,21 +1746,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1652,19 +1768,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bredmossen, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>626435</v>
+        <v>626601</v>
       </c>
       <c r="R10" t="n">
-        <v>6632380</v>
+        <v>6632105</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1688,22 +1809,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 dm2 på bark och naken ved på granlåga, omkr. 123 cm, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,66 +1830,95 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark och naken ved på granlåga, omkr. 123 cm.. # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137084427</t>
+          <t>https://artportalen.se/Sighting/137504101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137080889</v>
+        <v>137504104</v>
       </c>
       <c r="B11" t="n">
-        <v>92148</v>
+        <v>91667</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>5741</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bredmossen, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>626425</v>
+        <v>626669</v>
       </c>
       <c r="R11" t="n">
-        <v>6632440</v>
+        <v>6632080</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1800,22 +1945,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>6 ex. i mossvegetation under levande gran. Ca. 25 m ifrån avverkninganmält område.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,73 +1966,74 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre, grandominerad barrskog.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ebba Ganslandt</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ebba Ganslandt</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137080889</t>
+          <t>https://artportalen.se/Sighting/137504104</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137081807</v>
+        <v>137084688</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>97671</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bredmossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>626424</v>
+        <v>626425</v>
       </c>
       <c r="R12" t="n">
-        <v>6632421</v>
+        <v>6632382</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1921,7 +2062,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,7 +2072,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,16 +2103,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137081807</t>
+          <t>https://artportalen.se/Sighting/137084688</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137084761</v>
+        <v>137080859</v>
       </c>
       <c r="B13" t="n">
-        <v>93521</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,39 +2120,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bredmossen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>626398</v>
+        <v>626374</v>
       </c>
       <c r="R13" t="n">
-        <v>6632408</v>
+        <v>6632425</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2038,7 +2183,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,7 +2193,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2074,38 +2219,38 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137084761</t>
+          <t>https://artportalen.se/Sighting/137080859</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137080237</v>
+        <v>137085262</v>
       </c>
       <c r="B14" t="n">
-        <v>58032</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2113,20 +2258,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bredmossen, Skogstibble skjutfält, Upl</t>
+          <t>Bredmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>626384</v>
+        <v>626444</v>
       </c>
       <c r="R14" t="n">
-        <v>6632447</v>
+        <v>6632321</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2155,7 +2300,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,7 +2310,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,16 +2336,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137080237</t>
+          <t>https://artportalen.se/Sighting/137085262</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137084324</v>
+        <v>137504107</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>92186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,42 +2353,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bredmossen, Skogstibble skjutfält, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>626425</v>
+        <v>626671</v>
       </c>
       <c r="R15" t="n">
-        <v>6632432</v>
+        <v>6632200</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2270,102 +2416,107 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:55</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ganska säkra spår av födosökande tretåig hackspett på död gran där barken skalats av och många små hack och ”plockade” barkbitar nästan nere vid basen på trädet, vilket brukar vara typiskt för tretåig. Se bilder.</t>
+          <t>Ca. 3 dm2 på bark på granlåga, omkr. ca. 70 cm, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. ca. 70 cm.. # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137084324</t>
+          <t>https://artportalen.se/Sighting/137504107</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137081910</v>
+        <v>137084059</v>
       </c>
       <c r="B16" t="n">
-        <v>5188</v>
+        <v>92617</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bredmossen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>626431</v>
+        <v>626433</v>
       </c>
       <c r="R16" t="n">
-        <v>6632423</v>
+        <v>6632393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2397,7 +2548,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2407,7 +2558,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,54 +2573,54 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Ebba Ganslandt</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137081910</t>
+          <t>https://artportalen.se/Sighting/137084059</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137084894</v>
+        <v>137085040</v>
       </c>
       <c r="B17" t="n">
-        <v>101650</v>
+        <v>92617</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2479,13 +2630,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>626405</v>
+        <v>626417</v>
       </c>
       <c r="R17" t="n">
-        <v>6632381</v>
+        <v>6632346</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2514,7 +2665,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2524,7 +2675,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2550,54 +2701,59 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137084894</t>
+          <t>https://artportalen.se/Sighting/137085040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>89976105</v>
+        <v>137085258</v>
       </c>
       <c r="B18" t="n">
-        <v>98215</v>
+        <v>92617</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>569</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granbräken</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryopteris cristata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+          <t>Bredmossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>626519</v>
+        <v>626444</v>
       </c>
       <c r="R18" t="n">
-        <v>6631702</v>
+        <v>6632321</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2621,17 +2777,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2003-08-13</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2003-08-13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Litet bestånd.</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,54 +2807,54 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Olle Kvarnbäck</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89976105</t>
+          <t>https://artportalen.se/Sighting/137085258</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>74811574</v>
+        <v>137504097</v>
       </c>
       <c r="B19" t="n">
-        <v>80467</v>
+        <v>92618</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2707,10 +2868,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>626344</v>
+        <v>626325</v>
       </c>
       <c r="R19" t="n">
-        <v>6631739</v>
+        <v>6632016</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2737,17 +2898,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2003-08-13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2003-08-13</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2 dm2 på stammen av levande asp, omkr. 138 cm.</t>
+          <t>Ca. 40 dm2 på bark på granlåga, omkr. 110 cm, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2759,14 +2920,24 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>Asp</t>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stammen av levande asp. # Asp</t>
+          <t>Bark på granlåga, omkr. 110 cm.. # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2783,16 +2954,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/74811574</t>
+          <t>https://artportalen.se/Sighting/137504097</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>70080650</v>
+        <v>137504098</v>
       </c>
       <c r="B20" t="n">
-        <v>91930</v>
+        <v>92618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2800,43 +2971,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skogstibble, Upl</t>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>626184</v>
+        <v>626429</v>
       </c>
       <c r="R20" t="n">
-        <v>6631152</v>
+        <v>6632048</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2845,7 +3019,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Enköping</t>
+          <t>Uppsala</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2855,17 +3029,22 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Nysätra</t>
+          <t>Skogs-Tibble</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2018-03-20</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca. 3 dm2 på bark på avbruten stamdel från granhögstubbe, omkr. 128 cm, i avverkningsanmält område.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2874,23 +3053,3706 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark på avbruten stamdel från granhögstubbe, omkr. 128 cm.. # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Teresa Jonsson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Teresa Jonsson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504098</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137504105</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92618</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>626660</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6632189</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca. 5 dm2 på bark på granlåga, omkr. 97 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. 97 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504105</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137504106</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92618</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>626662</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6632192</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca. 20 dm2 på bark på granlåga, omkr. 103 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. 103 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504106</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137085272</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92399</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3008</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Timmerticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>626441</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6632320</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137085272</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137084427</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93497</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>626435</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6632380</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137084427</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137504108</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93157</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>626585</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6632239</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 ex. under gran.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Äldre, fuktig granskog med inslag av lövträd.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504108</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137080889</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92148</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>626425</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6632440</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080889</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137081807</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>626424</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6632421</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137081807</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137084761</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93521</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>626398</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6632408</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137084761</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137504109</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93522</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>626588</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6632237</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>4 ex. under gran.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Äldre, fuktig granskog med inslag av lövträd.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504109</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137080237</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bredmossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>626384</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6632447</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137080237</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137084324</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bredmossen, Skogstibble skjutfält, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>626425</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6632432</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ganska säkra spår av födosökande tretåig hackspett på död gran där barken skalats av och många små hack och ”plockade” barkbitar nästan nere vid basen på trädet, vilket brukar vara typiskt för tretåig. Se bilder.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137084324</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137081910</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5188</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>626431</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6632423</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137081910</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137084894</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101650</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bredmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>626405</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6632381</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137084894</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137504118</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92618</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>625885</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6632093</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca. 10 dm2 på bark på granlåga, omkr. 113 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. 113 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504118</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137504119</v>
+      </c>
+      <c r="B35" t="n">
+        <v>92860</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>625740</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6631978</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gamla fruktkroppar på granlåga, omkr. 76 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Granlåga, omkr. 76 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504119</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137504120</v>
+      </c>
+      <c r="B36" t="n">
+        <v>92860</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>625741</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6631947</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Några gamla fruktkroppar på granlåga, omkr. 112 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Granlåga, omkr. 112 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504120</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137504090</v>
+      </c>
+      <c r="B37" t="n">
+        <v>6834</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100763</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Cinnoberbagge</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cucujus cinnaberinus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>625974</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6631866</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1 larv under bark på asplåga, omkr. 132 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504090</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137504091</v>
+      </c>
+      <c r="B38" t="n">
+        <v>6834</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100763</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Cinnoberbagge</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Cucujus cinnaberinus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>625971</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6631882</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1 larv under bark på avbruten stamdel från asphögstubbe, omkr. 64 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504091</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137504094</v>
+      </c>
+      <c r="B39" t="n">
+        <v>92986</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>366</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>626010</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6631987</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>2 ex. på naken ved på asplåga, omkr. 40 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Naken ved på asplåga, omkr. 40 cm.. # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504094</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137504093</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92186</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>625977</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6631945</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1 dm2 på bark på granlåga, omkr, 54 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr, 54 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504093</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137504095</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92186</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>626163</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6632017</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ca. 5 dm2 på bark på granlåga, omkr. 89 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. 89 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504095</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137504096</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92186</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>626155</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6632018</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ca. 10 dm2 på bark på granlåga, omkr. 98 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. 98 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504096</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>89976105</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98215</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>569</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Granbräken</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryopteris cristata</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>626519</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6631702</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2003-08-13</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2003-08-13</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Litet bestånd.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89976105</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137504124</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92457</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>658</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>626064</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6631586</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ca. 5 ex. på granlåga, omkr. 95 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Granlåga, omkr. 95 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504124</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>137504121</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92618</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>626046</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6631596</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ca. 5 dm2 på bark på granlåga, omkr. ca. 80 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. ca. 80 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504121</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>137504122</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92618</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>626060</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6631584</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ca. 10 dm2 på bark och naken ved på granlåga, omkr. 113 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark och naken ved på granlåga, omkr. 113 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504122</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137504123</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92618</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>626064</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6631586</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ca. 10 dm2 på bark på granlåga, omkr. 95 cm, i avverkningsanmält område.</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Äldre, naturskogsartad skog , bitvis med mycket död, stående och liggande gran, samt med varierat inslag av tall, lövträd och levande granar.</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Bark på granlåga, omkr. 95 cm.. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504123</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>74811574</v>
+      </c>
+      <c r="B48" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Skogstibble övningsfält, vid Degermossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>626344</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6631739</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Skogs-Tibble</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2003-08-13</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2003-08-13</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>2 dm2 på stammen av levande asp, omkr. 138 cm.</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stammen av levande asp. # Asp</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74811574</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>70080650</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skogstibble, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>626184</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6631152</v>
+      </c>
+      <c r="S49" t="n">
+        <v>50</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Enköping</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2018-03-20</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Teresa Jonsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Teresa Jonsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/70080650</t>
         </is>
@@ -2917,6 +6779,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
